--- a/artfynd/A 22371-2025 artfynd.xlsx
+++ b/artfynd/A 22371-2025 artfynd.xlsx
@@ -1079,45 +1079,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131737917</v>
+        <v>131737369</v>
       </c>
       <c r="B6" t="n">
-        <v>8453</v>
+        <v>91881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken Sydväst, Vb</t>
+          <t>Trehörningstjärnheden Nord, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719405</v>
+        <v>719649</v>
       </c>
       <c r="R6" t="n">
-        <v>7172122</v>
+        <v>7172012</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131737369</v>
+        <v>131737370</v>
       </c>
       <c r="B7" t="n">
         <v>91881</v>
@@ -1211,14 +1211,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nord, Vb</t>
+          <t>Trehörningstjärnheden Nordväst, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719649</v>
+        <v>719671</v>
       </c>
       <c r="R7" t="n">
-        <v>7172012</v>
+        <v>7172010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,45 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131737370</v>
+        <v>131737917</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>8453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nordväst, Vb</t>
+          <t>Kroktjärnbäcken Sydväst, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>719671</v>
+        <v>719405</v>
       </c>
       <c r="R8" t="n">
-        <v>7172010</v>
+        <v>7172122</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 22371-2025 artfynd.xlsx
+++ b/artfynd/A 22371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737371</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739271</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>79851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131733259</v>
       </c>
       <c r="B4" t="n">
-        <v>78267</v>
+        <v>78268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131734647</v>
       </c>
       <c r="B5" t="n">
-        <v>79017</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>131737369</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131737370</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>131737917</v>
       </c>
       <c r="B8" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>131734649</v>
       </c>
       <c r="B9" t="n">
-        <v>79017</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>131733398</v>
       </c>
       <c r="B10" t="n">
-        <v>78663</v>
+        <v>78664</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131738962</v>
       </c>
       <c r="B11" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131737149</v>
       </c>
       <c r="B12" t="n">
-        <v>5493</v>
+        <v>5494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>131734648</v>
       </c>
       <c r="B13" t="n">
-        <v>79017</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>131737916</v>
       </c>
       <c r="B14" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22371-2025 artfynd.xlsx
+++ b/artfynd/A 22371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737371</v>
       </c>
       <c r="B2" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739271</v>
       </c>
       <c r="B3" t="n">
-        <v>79851</v>
+        <v>79854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131733259</v>
       </c>
       <c r="B4" t="n">
-        <v>78268</v>
+        <v>78271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131734647</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,45 +1079,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131737369</v>
+        <v>131737917</v>
       </c>
       <c r="B6" t="n">
-        <v>91882</v>
+        <v>8454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nord, Vb</t>
+          <t>Kroktjärnbäcken Sydväst, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719649</v>
+        <v>719405</v>
       </c>
       <c r="R6" t="n">
-        <v>7172012</v>
+        <v>7172122</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131737370</v>
+        <v>131737369</v>
       </c>
       <c r="B7" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,14 +1211,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nordväst, Vb</t>
+          <t>Trehörningstjärnheden Nord, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719671</v>
+        <v>719649</v>
       </c>
       <c r="R7" t="n">
-        <v>7172010</v>
+        <v>7172012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,45 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131737917</v>
+        <v>131737370</v>
       </c>
       <c r="B8" t="n">
-        <v>8454</v>
+        <v>91885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken Sydväst, Vb</t>
+          <t>Trehörningstjärnheden Nordväst, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>719405</v>
+        <v>719671</v>
       </c>
       <c r="R8" t="n">
-        <v>7172122</v>
+        <v>7172010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,7 +1385,7 @@
         <v>131734649</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>131733398</v>
       </c>
       <c r="B10" t="n">
-        <v>78664</v>
+        <v>78667</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131738962</v>
       </c>
       <c r="B11" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>131734648</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22371-2025 artfynd.xlsx
+++ b/artfynd/A 22371-2025 artfynd.xlsx
@@ -1079,45 +1079,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131737917</v>
+        <v>131737369</v>
       </c>
       <c r="B6" t="n">
-        <v>8454</v>
+        <v>91885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken Sydväst, Vb</t>
+          <t>Trehörningstjärnheden Nord, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719405</v>
+        <v>719649</v>
       </c>
       <c r="R6" t="n">
-        <v>7172122</v>
+        <v>7172012</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131737369</v>
+        <v>131737370</v>
       </c>
       <c r="B7" t="n">
         <v>91885</v>
@@ -1211,14 +1211,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nord, Vb</t>
+          <t>Trehörningstjärnheden Nordväst, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719649</v>
+        <v>719671</v>
       </c>
       <c r="R7" t="n">
-        <v>7172012</v>
+        <v>7172010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,45 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131737370</v>
+        <v>131737917</v>
       </c>
       <c r="B8" t="n">
-        <v>91885</v>
+        <v>8454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nordväst, Vb</t>
+          <t>Kroktjärnbäcken Sydväst, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>719671</v>
+        <v>719405</v>
       </c>
       <c r="R8" t="n">
-        <v>7172010</v>
+        <v>7172122</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 22371-2025 artfynd.xlsx
+++ b/artfynd/A 22371-2025 artfynd.xlsx
@@ -1180,45 +1180,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131737370</v>
+        <v>131737917</v>
       </c>
       <c r="B7" t="n">
-        <v>91885</v>
+        <v>8454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nordväst, Vb</t>
+          <t>Kroktjärnbäcken Sydväst, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719671</v>
+        <v>719405</v>
       </c>
       <c r="R7" t="n">
-        <v>7172010</v>
+        <v>7172122</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,45 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131737917</v>
+        <v>131737370</v>
       </c>
       <c r="B8" t="n">
-        <v>8454</v>
+        <v>91885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken Sydväst, Vb</t>
+          <t>Trehörningstjärnheden Nordväst, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>719405</v>
+        <v>719671</v>
       </c>
       <c r="R8" t="n">
-        <v>7172122</v>
+        <v>7172010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 22371-2025 artfynd.xlsx
+++ b/artfynd/A 22371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737371</v>
       </c>
       <c r="B2" t="n">
-        <v>91885</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739271</v>
       </c>
       <c r="B3" t="n">
-        <v>79854</v>
+        <v>79856</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131733259</v>
       </c>
       <c r="B4" t="n">
-        <v>78271</v>
+        <v>78273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131734647</v>
       </c>
       <c r="B5" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>131737369</v>
       </c>
       <c r="B6" t="n">
-        <v>91885</v>
+        <v>91891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,45 +1180,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131737917</v>
+        <v>131737370</v>
       </c>
       <c r="B7" t="n">
-        <v>8454</v>
+        <v>91891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken Sydväst, Vb</t>
+          <t>Trehörningstjärnheden Nordväst, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719405</v>
+        <v>719671</v>
       </c>
       <c r="R7" t="n">
-        <v>7172122</v>
+        <v>7172010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,45 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131737370</v>
+        <v>131737917</v>
       </c>
       <c r="B8" t="n">
-        <v>91885</v>
+        <v>8454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nordväst, Vb</t>
+          <t>Kroktjärnbäcken Sydväst, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>719671</v>
+        <v>719405</v>
       </c>
       <c r="R8" t="n">
-        <v>7172010</v>
+        <v>7172122</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,7 +1385,7 @@
         <v>131734649</v>
       </c>
       <c r="B9" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>131733398</v>
       </c>
       <c r="B10" t="n">
-        <v>78667</v>
+        <v>78669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131738962</v>
       </c>
       <c r="B11" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>131734648</v>
       </c>
       <c r="B13" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22371-2025 artfynd.xlsx
+++ b/artfynd/A 22371-2025 artfynd.xlsx
@@ -1079,45 +1079,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131737369</v>
+        <v>131737917</v>
       </c>
       <c r="B6" t="n">
-        <v>91891</v>
+        <v>8454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nord, Vb</t>
+          <t>Kroktjärnbäcken Sydväst, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719649</v>
+        <v>719405</v>
       </c>
       <c r="R6" t="n">
-        <v>7172012</v>
+        <v>7172122</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131737370</v>
+        <v>131737369</v>
       </c>
       <c r="B7" t="n">
         <v>91891</v>
@@ -1211,14 +1211,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nordväst, Vb</t>
+          <t>Trehörningstjärnheden Nord, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719671</v>
+        <v>719649</v>
       </c>
       <c r="R7" t="n">
-        <v>7172010</v>
+        <v>7172012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,45 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131737917</v>
+        <v>131737370</v>
       </c>
       <c r="B8" t="n">
-        <v>8454</v>
+        <v>91891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken Sydväst, Vb</t>
+          <t>Trehörningstjärnheden Nordväst, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>719405</v>
+        <v>719671</v>
       </c>
       <c r="R8" t="n">
-        <v>7172122</v>
+        <v>7172010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 22371-2025 artfynd.xlsx
+++ b/artfynd/A 22371-2025 artfynd.xlsx
@@ -1079,45 +1079,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131737917</v>
+        <v>131737369</v>
       </c>
       <c r="B6" t="n">
-        <v>8454</v>
+        <v>91891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken Sydväst, Vb</t>
+          <t>Trehörningstjärnheden Nord, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719405</v>
+        <v>719649</v>
       </c>
       <c r="R6" t="n">
-        <v>7172122</v>
+        <v>7172012</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131737369</v>
+        <v>131737370</v>
       </c>
       <c r="B7" t="n">
         <v>91891</v>
@@ -1211,14 +1211,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nord, Vb</t>
+          <t>Trehörningstjärnheden Nordväst, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719649</v>
+        <v>719671</v>
       </c>
       <c r="R7" t="n">
-        <v>7172012</v>
+        <v>7172010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,45 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131737370</v>
+        <v>131737917</v>
       </c>
       <c r="B8" t="n">
-        <v>91891</v>
+        <v>8454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nordväst, Vb</t>
+          <t>Kroktjärnbäcken Sydväst, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>719671</v>
+        <v>719405</v>
       </c>
       <c r="R8" t="n">
-        <v>7172010</v>
+        <v>7172122</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 22371-2025 artfynd.xlsx
+++ b/artfynd/A 22371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737371</v>
       </c>
       <c r="B2" t="n">
-        <v>91942</v>
+        <v>91945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739271</v>
       </c>
       <c r="B3" t="n">
-        <v>79905</v>
+        <v>79907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131733259</v>
       </c>
       <c r="B4" t="n">
-        <v>78322</v>
+        <v>78324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131734647</v>
       </c>
       <c r="B5" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,45 +1079,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131737917</v>
+        <v>131737369</v>
       </c>
       <c r="B6" t="n">
-        <v>8455</v>
+        <v>91945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken Sydväst, Vb</t>
+          <t>Trehörningstjärnheden Nord, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719405</v>
+        <v>719649</v>
       </c>
       <c r="R6" t="n">
-        <v>7172122</v>
+        <v>7172012</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131737369</v>
+        <v>131737370</v>
       </c>
       <c r="B7" t="n">
-        <v>91942</v>
+        <v>91945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,14 +1211,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nord, Vb</t>
+          <t>Trehörningstjärnheden Nordväst, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719649</v>
+        <v>719671</v>
       </c>
       <c r="R7" t="n">
-        <v>7172012</v>
+        <v>7172010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,45 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131737370</v>
+        <v>131737917</v>
       </c>
       <c r="B8" t="n">
-        <v>91942</v>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nordväst, Vb</t>
+          <t>Kroktjärnbäcken Sydväst, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>719671</v>
+        <v>719405</v>
       </c>
       <c r="R8" t="n">
-        <v>7172010</v>
+        <v>7172122</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,7 +1385,7 @@
         <v>131734649</v>
       </c>
       <c r="B9" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>131733398</v>
       </c>
       <c r="B10" t="n">
-        <v>78718</v>
+        <v>78720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>131738962</v>
       </c>
       <c r="B11" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>131734648</v>
       </c>
       <c r="B13" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22371-2025 artfynd.xlsx
+++ b/artfynd/A 22371-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131737371</v>
+        <v>131737369</v>
       </c>
       <c r="B2" t="n">
-        <v>91945</v>
+        <v>92027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>719685</v>
+        <v>719649</v>
       </c>
       <c r="R2" t="n">
-        <v>7171957</v>
+        <v>7172012</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131739271</v>
+        <v>131737370</v>
       </c>
       <c r="B3" t="n">
-        <v>79907</v>
+        <v>92027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken Sydväst, Vb</t>
+          <t>Trehörningstjärnheden Nordväst, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>719424</v>
+        <v>719671</v>
       </c>
       <c r="R3" t="n">
-        <v>7172064</v>
+        <v>7172010</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131733259</v>
+        <v>131737371</v>
       </c>
       <c r="B4" t="n">
-        <v>78324</v>
+        <v>92027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken Sydväst, Vb</t>
+          <t>Trehörningstjärnheden Nord, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>719426</v>
+        <v>719685</v>
       </c>
       <c r="R4" t="n">
-        <v>7172065</v>
+        <v>7171957</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131734647</v>
+        <v>131733398</v>
       </c>
       <c r="B5" t="n">
-        <v>79074</v>
+        <v>78776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>719427</v>
+        <v>719349</v>
       </c>
       <c r="R5" t="n">
-        <v>7172054</v>
+        <v>7172053</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131737369</v>
+        <v>131734647</v>
       </c>
       <c r="B6" t="n">
-        <v>91945</v>
+        <v>79130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,34 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nord, Vb</t>
+          <t>Kroktjärnbäcken Sydväst, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719649</v>
+        <v>719427</v>
       </c>
       <c r="R6" t="n">
-        <v>7172012</v>
+        <v>7172054</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131737370</v>
+        <v>131734649</v>
       </c>
       <c r="B7" t="n">
-        <v>91945</v>
+        <v>79130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden Nordväst, Vb</t>
+          <t>Kroktjärnbäcken Sydväst, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719671</v>
+        <v>719346</v>
       </c>
       <c r="R7" t="n">
-        <v>7172010</v>
+        <v>7172056</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131737917</v>
+        <v>131738962</v>
       </c>
       <c r="B8" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>719405</v>
+        <v>719488</v>
       </c>
       <c r="R8" t="n">
-        <v>7172122</v>
+        <v>7172073</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131734649</v>
+        <v>131733259</v>
       </c>
       <c r="B9" t="n">
-        <v>79074</v>
+        <v>78377</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>719346</v>
+        <v>719426</v>
       </c>
       <c r="R9" t="n">
-        <v>7172056</v>
+        <v>7172065</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131733398</v>
+        <v>131737149</v>
       </c>
       <c r="B10" t="n">
-        <v>78720</v>
+        <v>5497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>101410</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>719349</v>
+        <v>719339</v>
       </c>
       <c r="R10" t="n">
         <v>7172053</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131738962</v>
+        <v>131737916</v>
       </c>
       <c r="B11" t="n">
-        <v>79936</v>
+        <v>8460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>719488</v>
+        <v>719417</v>
       </c>
       <c r="R11" t="n">
-        <v>7172073</v>
+        <v>7172043</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131737149</v>
+        <v>131739271</v>
       </c>
       <c r="B12" t="n">
-        <v>5495</v>
+        <v>79963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>719339</v>
+        <v>719424</v>
       </c>
       <c r="R12" t="n">
-        <v>7172053</v>
+        <v>7172064</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
         <v>131734648</v>
       </c>
       <c r="B13" t="n">
-        <v>79074</v>
+        <v>79130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131737916</v>
+        <v>131737917</v>
       </c>
       <c r="B14" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>719417</v>
+        <v>719405</v>
       </c>
       <c r="R14" t="n">
-        <v>7172043</v>
+        <v>7172122</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 22371-2025 artfynd.xlsx
+++ b/artfynd/A 22371-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737369</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737370</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737371</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733398</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734647</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734648</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734649</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738962</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733259</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737149</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737916</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737917</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,8 +2050,28 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739271</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>